--- a/Sample_Project/設計書/B1_顧客管理システム/030_アプリ設計/110_テスト仕様書/単体テスト仕様書(Webサービス)_B10103_顧客登録.xlsx
+++ b/Sample_Project/設計書/B1_顧客管理システム/030_アプリ設計/110_テスト仕様書/単体テスト仕様書(Webサービス)_B10103_顧客登録.xlsx
@@ -12199,8 +12199,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -12241,8 +12241,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -12277,8 +12277,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -12315,8 +12315,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -12349,8 +12349,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -12383,8 +12383,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -12417,8 +12417,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -12451,8 +12451,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -12489,8 +12489,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -12523,8 +12523,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -12557,8 +12557,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -12593,8 +12593,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -12627,8 +12627,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -12661,8 +12661,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -12695,8 +12695,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -12733,8 +12733,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -12767,8 +12767,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -12805,8 +12805,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -12839,8 +12839,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -12875,8 +12875,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -12909,8 +12909,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -12943,8 +12943,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -12977,8 +12977,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -13013,8 +13013,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -13047,8 +13047,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -13083,8 +13083,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -13123,8 +13123,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -13157,8 +13157,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -13191,8 +13191,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -13225,8 +13225,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -13265,8 +13265,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -13313,8 +13313,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-3-1</v>
       </c>
@@ -13349,8 +13349,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-4-1</v>
       </c>
@@ -13397,8 +13397,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -13439,8 +13439,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -13473,8 +13473,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -13507,8 +13507,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -13543,8 +13543,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -13577,8 +13577,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -13611,8 +13611,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -13647,8 +13647,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -13681,8 +13681,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -13717,8 +13717,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -13751,8 +13751,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -13785,8 +13785,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -13819,8 +13819,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -13853,8 +13853,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -13887,8 +13887,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -13923,8 +13923,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -13959,8 +13959,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -13995,8 +13995,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -14033,8 +14033,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -14067,8 +14067,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -14101,8 +14101,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -14135,8 +14135,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -14169,8 +14169,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -14205,8 +14205,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -14239,8 +14239,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -14273,8 +14273,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -14307,8 +14307,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -14341,8 +14341,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -14375,8 +14375,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -14409,8 +14409,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -14443,8 +14443,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -14479,8 +14479,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -14515,8 +14515,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -14549,8 +14549,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -14583,8 +14583,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -14617,8 +14617,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -14651,8 +14651,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -14691,8 +14691,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -14725,8 +14725,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -14761,8 +14761,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -14797,8 +14797,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -14831,8 +14831,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -14867,8 +14867,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -14903,8 +14903,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -14943,8 +14943,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -14979,8 +14979,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -15015,8 +15015,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -15055,8 +15055,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -15089,8 +15089,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -15125,8 +15125,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -15161,8 +15161,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -15195,8 +15195,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -15231,8 +15231,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -15271,8 +15271,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -15305,8 +15305,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -15339,8 +15339,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -15373,8 +15373,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -15407,8 +15407,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -15443,8 +15443,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -15477,8 +15477,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -15511,8 +15511,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -15545,8 +15545,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -15579,8 +15579,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -15615,8 +15615,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -15657,8 +15657,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -15697,8 +15697,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -15731,8 +15731,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -15771,8 +15771,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -15811,8 +15811,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -15845,8 +15845,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -15887,8 +15887,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -15923,8 +15923,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -15957,8 +15957,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -15991,8 +15991,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -16027,8 +16027,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -16061,8 +16061,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -16095,8 +16095,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -16129,8 +16129,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -16163,8 +16163,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -16199,8 +16199,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -16233,8 +16233,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -16267,8 +16267,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -16301,8 +16301,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -16335,8 +16335,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -16371,8 +16371,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -16409,8 +16409,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -16449,8 +16449,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -16485,8 +16485,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -16519,8 +16519,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -16553,8 +16553,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -16595,8 +16595,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -16631,8 +16631,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -16665,8 +16665,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -16699,8 +16699,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -16735,8 +16735,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -16769,8 +16769,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -16807,8 +16807,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -16847,8 +16847,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -16883,8 +16883,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -16919,8 +16919,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -16955,8 +16955,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -16991,8 +16991,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -17027,8 +17027,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -17061,8 +17061,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -17095,8 +17095,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -17129,8 +17129,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -17163,8 +17163,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -17197,8 +17197,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -17235,8 +17235,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -17269,8 +17269,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -17305,8 +17305,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -17339,8 +17339,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -17373,8 +17373,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -17407,8 +17407,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -17441,8 +17441,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -17475,8 +17475,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -17509,8 +17509,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -17543,8 +17543,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -17577,8 +17577,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -17611,8 +17611,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -17645,8 +17645,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -17681,8 +17681,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -17715,8 +17715,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -17749,8 +17749,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -17783,8 +17783,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -17817,8 +17817,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -17851,8 +17851,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -17885,8 +17885,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -17921,8 +17921,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -17955,8 +17955,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -17989,8 +17989,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -18023,8 +18023,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -18057,8 +18057,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -18091,8 +18091,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -18125,8 +18125,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -18159,8 +18159,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -18193,8 +18193,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -18229,8 +18229,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -18265,8 +18265,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -18307,8 +18307,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -18345,8 +18345,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -18383,8 +18383,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -18425,8 +18425,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -18461,8 +18461,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -18495,8 +18495,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -18531,8 +18531,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -18565,8 +18565,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -18603,8 +18603,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -18643,8 +18643,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -18677,8 +18677,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -18711,8 +18711,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -18745,8 +18745,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -18779,8 +18779,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -18813,8 +18813,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -18847,8 +18847,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -18883,8 +18883,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -18921,8 +18921,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -18955,8 +18955,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -18989,8 +18989,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -19023,8 +19023,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -19057,8 +19057,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -19091,8 +19091,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -19125,8 +19125,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -19159,8 +19159,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -19193,8 +19193,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -19227,8 +19227,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -19261,8 +19261,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -19295,8 +19295,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -19329,8 +19329,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -19367,8 +19367,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -19401,8 +19401,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -19435,8 +19435,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -19469,8 +19469,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -19503,8 +19503,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -19537,8 +19537,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -19571,8 +19571,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -19605,8 +19605,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -19639,8 +19639,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -19673,8 +19673,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -19707,8 +19707,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -19741,8 +19741,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -19775,8 +19775,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -19809,8 +19809,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -19843,8 +19843,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -19879,8 +19879,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -19913,8 +19913,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -19947,8 +19947,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -19983,8 +19983,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -20019,8 +20019,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -20061,8 +20061,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -20097,8 +20097,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -20131,8 +20131,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -20165,8 +20165,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -20199,8 +20199,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -20233,8 +20233,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -20269,8 +20269,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -20303,8 +20303,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -20337,8 +20337,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -20371,8 +20371,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -20405,8 +20405,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -20441,8 +20441,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -20481,8 +20481,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -20523,8 +20523,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -20557,8 +20557,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -20595,8 +20595,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -20629,8 +20629,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -20669,8 +20669,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -20705,8 +20705,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -20741,8 +20741,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -20777,8 +20777,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -20815,8 +20815,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -20849,8 +20849,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -20885,8 +20885,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -20919,8 +20919,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -20953,8 +20953,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -20987,8 +20987,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -21021,8 +21021,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -21055,8 +21055,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -21089,8 +21089,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -21123,8 +21123,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -21157,8 +21157,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -21191,8 +21191,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -21225,8 +21225,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -21261,8 +21261,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -21295,8 +21295,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -21329,8 +21329,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -21363,8 +21363,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -21397,8 +21397,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -21431,8 +21431,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -21467,8 +21467,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -21501,8 +21501,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -21535,8 +21535,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -21569,8 +21569,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -21603,8 +21603,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -21637,8 +21637,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -21671,8 +21671,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -21705,8 +21705,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -21741,8 +21741,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -21783,8 +21783,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -21817,8 +21817,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -21851,8 +21851,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -21885,8 +21885,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -21925,8 +21925,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -21961,8 +21961,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -21997,8 +21997,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -22033,8 +22033,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -22071,8 +22071,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -22105,8 +22105,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -22139,8 +22139,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -22173,8 +22173,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -22207,8 +22207,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -22241,8 +22241,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -22275,8 +22275,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F296),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F296)&gt;0)*ROW($F$11:F296),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J296),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -22309,8 +22309,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F297),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F297)&gt;0)*ROW($F$11:F297),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J297),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -22501,8 +22501,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -22543,8 +22543,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -22579,8 +22579,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -22617,8 +22617,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -22651,8 +22651,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -22685,8 +22685,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -22719,8 +22719,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -22753,8 +22753,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -22791,8 +22791,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -22825,8 +22825,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -22859,8 +22859,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -22895,8 +22895,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -22929,8 +22929,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -22963,8 +22963,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -22997,8 +22997,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -23035,8 +23035,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -23069,8 +23069,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -23107,8 +23107,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -23141,8 +23141,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -23177,8 +23177,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -23211,8 +23211,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -23245,8 +23245,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -23279,8 +23279,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -23315,8 +23315,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -23349,8 +23349,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -23385,8 +23385,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -23425,8 +23425,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -23459,8 +23459,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -23493,8 +23493,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -23527,8 +23527,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -23565,8 +23565,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -23599,8 +23599,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -23641,8 +23641,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -23675,8 +23675,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -23709,8 +23709,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -23745,8 +23745,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -23779,8 +23779,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -23813,8 +23813,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -23849,8 +23849,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -23883,8 +23883,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -23919,8 +23919,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -23953,8 +23953,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -23987,8 +23987,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -24021,8 +24021,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -24055,8 +24055,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -24089,8 +24089,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -24125,8 +24125,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -24161,8 +24161,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -24197,8 +24197,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -24235,8 +24235,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -24269,8 +24269,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -24303,8 +24303,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -24337,8 +24337,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -24371,8 +24371,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -24407,8 +24407,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -24441,8 +24441,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -24475,8 +24475,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -24509,8 +24509,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -24543,8 +24543,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -24577,8 +24577,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -24611,8 +24611,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -24645,8 +24645,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -24681,8 +24681,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -24717,8 +24717,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -24751,8 +24751,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -24785,8 +24785,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -24819,8 +24819,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -24853,8 +24853,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -24893,8 +24893,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -24927,8 +24927,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -24963,8 +24963,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -24999,8 +24999,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -25033,8 +25033,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -25069,8 +25069,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -25105,8 +25105,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -25145,8 +25145,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -25181,8 +25181,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -25217,8 +25217,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -25257,8 +25257,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -25291,8 +25291,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -25327,8 +25327,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -25363,8 +25363,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -25397,8 +25397,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -25433,8 +25433,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -25473,8 +25473,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -25507,8 +25507,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -25541,8 +25541,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -25575,8 +25575,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -25609,8 +25609,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -25645,8 +25645,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -25679,8 +25679,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -25713,8 +25713,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -25747,8 +25747,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -25781,8 +25781,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -25817,8 +25817,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -25859,8 +25859,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -25899,8 +25899,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -25933,8 +25933,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -25973,8 +25973,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -26013,8 +26013,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -26047,8 +26047,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -26089,8 +26089,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -26125,8 +26125,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -26159,8 +26159,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -26193,8 +26193,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -26229,8 +26229,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -26263,8 +26263,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -26297,8 +26297,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -26331,8 +26331,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -26365,8 +26365,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -26401,8 +26401,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -26435,8 +26435,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -26469,8 +26469,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -26503,8 +26503,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -26537,8 +26537,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -26573,8 +26573,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -26611,8 +26611,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -26651,8 +26651,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -26687,8 +26687,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -26721,8 +26721,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -26755,8 +26755,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -26797,8 +26797,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -26833,8 +26833,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -26867,8 +26867,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -26901,8 +26901,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -26937,8 +26937,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -26971,8 +26971,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -27009,8 +27009,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -27049,8 +27049,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -27085,8 +27085,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -27121,8 +27121,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -27157,8 +27157,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -27193,8 +27193,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -27229,8 +27229,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -27263,8 +27263,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -27297,8 +27297,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -27331,8 +27331,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -27365,8 +27365,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -27399,8 +27399,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -27437,8 +27437,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -27471,8 +27471,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -27507,8 +27507,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -27541,8 +27541,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -27575,8 +27575,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -27609,8 +27609,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -27643,8 +27643,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -27677,8 +27677,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -27711,8 +27711,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -27745,8 +27745,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -27779,8 +27779,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -27813,8 +27813,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -27847,8 +27847,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -27883,8 +27883,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -27917,8 +27917,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -27951,8 +27951,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -27985,8 +27985,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -28019,8 +28019,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -28053,8 +28053,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -28087,8 +28087,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -28123,8 +28123,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -28157,8 +28157,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -28191,8 +28191,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -28225,8 +28225,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -28259,8 +28259,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -28293,8 +28293,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -28327,8 +28327,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -28361,8 +28361,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -28395,8 +28395,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -28431,8 +28431,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -28467,8 +28467,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -28509,8 +28509,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -28547,8 +28547,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -28585,8 +28585,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -28627,8 +28627,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -28663,8 +28663,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -28697,8 +28697,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -28733,8 +28733,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -28767,8 +28767,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -28805,8 +28805,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -28845,8 +28845,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -28879,8 +28879,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -28913,8 +28913,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -28947,8 +28947,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -28981,8 +28981,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -29015,8 +29015,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -29049,8 +29049,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -29085,8 +29085,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -29123,8 +29123,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -29157,8 +29157,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -29191,8 +29191,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -29225,8 +29225,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -29259,8 +29259,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -29293,8 +29293,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -29327,8 +29327,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -29361,8 +29361,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -29395,8 +29395,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -29429,8 +29429,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -29463,8 +29463,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -29497,8 +29497,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -29531,8 +29531,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -29569,8 +29569,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -29603,8 +29603,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -29637,8 +29637,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -29671,8 +29671,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -29705,8 +29705,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -29739,8 +29739,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -29773,8 +29773,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -29807,8 +29807,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -29841,8 +29841,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -29875,8 +29875,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -29909,8 +29909,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -29943,8 +29943,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -29977,8 +29977,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -30011,8 +30011,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -30045,8 +30045,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -30081,8 +30081,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -30115,8 +30115,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -30149,8 +30149,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -30185,8 +30185,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -30221,8 +30221,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -30263,8 +30263,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -30299,8 +30299,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -30333,8 +30333,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -30367,8 +30367,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -30401,8 +30401,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -30435,8 +30435,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -30471,8 +30471,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -30505,8 +30505,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -30539,8 +30539,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -30573,8 +30573,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -30607,8 +30607,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -30643,8 +30643,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -30683,8 +30683,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -30725,8 +30725,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -30759,8 +30759,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -30797,8 +30797,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -30831,8 +30831,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -30871,8 +30871,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -30907,8 +30907,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -30943,8 +30943,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -30979,8 +30979,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -31017,8 +31017,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -31051,8 +31051,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -31087,8 +31087,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -31121,8 +31121,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -31155,8 +31155,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -31189,8 +31189,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -31223,8 +31223,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -31257,8 +31257,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -31291,8 +31291,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -31325,8 +31325,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -31359,8 +31359,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -31393,8 +31393,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -31427,8 +31427,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -31463,8 +31463,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -31497,8 +31497,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -31531,8 +31531,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -31565,8 +31565,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -31599,8 +31599,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -31633,8 +31633,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -31669,8 +31669,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -31703,8 +31703,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -31737,8 +31737,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -31771,8 +31771,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -31805,8 +31805,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -31839,8 +31839,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -31873,8 +31873,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -31907,8 +31907,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -31943,8 +31943,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -31985,8 +31985,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -32019,8 +32019,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -32053,8 +32053,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -32087,8 +32087,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -32127,8 +32127,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -32163,8 +32163,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -32199,8 +32199,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -32235,8 +32235,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -32273,8 +32273,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -32307,8 +32307,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -32341,8 +32341,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -32375,8 +32375,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -32409,8 +32409,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -32443,8 +32443,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -32477,8 +32477,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -32511,8 +32511,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -32719,8 +32719,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -32762,8 +32762,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -32799,8 +32799,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -32838,8 +32838,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -32873,8 +32873,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -32908,8 +32908,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -32943,8 +32943,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -32978,8 +32978,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -33017,8 +33017,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -33052,8 +33052,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -33087,8 +33087,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -33124,8 +33124,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -33159,8 +33159,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -33194,8 +33194,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -33229,8 +33229,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -33268,8 +33268,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -33303,8 +33303,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -33342,8 +33342,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -33377,8 +33377,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -33414,8 +33414,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -33449,8 +33449,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -33484,8 +33484,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -33519,8 +33519,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -33556,8 +33556,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -33591,8 +33591,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -33628,8 +33628,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -33669,8 +33669,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -33704,8 +33704,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -33739,8 +33739,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -33774,8 +33774,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -33813,8 +33813,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -33848,8 +33848,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -33903,8 +33903,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -33952,8 +33952,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -34005,8 +34005,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -34054,8 +34054,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -34097,8 +34097,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -34132,8 +34132,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-3-1</v>
       </c>
@@ -34167,8 +34167,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -34204,8 +34204,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -34239,8 +34239,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -34274,8 +34274,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -34311,8 +34311,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-2-1</v>
       </c>
@@ -34346,8 +34346,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -34383,8 +34383,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-2-1</v>
       </c>
@@ -34418,8 +34418,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-3-1</v>
       </c>
@@ -34453,8 +34453,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-4-1</v>
       </c>
@@ -34488,8 +34488,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-5-1</v>
       </c>
@@ -34523,8 +34523,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-6-1</v>
       </c>
@@ -34558,8 +34558,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -34595,8 +34595,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -34632,8 +34632,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -34669,8 +34669,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -34722,8 +34722,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-2-1</v>
       </c>
@@ -34757,8 +34757,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-3-1</v>
       </c>
@@ -34792,8 +34792,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-4-1</v>
       </c>
@@ -34827,8 +34827,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-5-1</v>
       </c>
@@ -34862,8 +34862,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -34899,8 +34899,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -34934,8 +34934,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -34969,8 +34969,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -35004,8 +35004,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -35039,8 +35039,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-6-1</v>
       </c>
@@ -35074,8 +35074,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-7-1</v>
       </c>
@@ -35109,8 +35109,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-8-1</v>
       </c>
@@ -35144,8 +35144,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -35195,8 +35195,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-2</v>
       </c>
@@ -35242,8 +35242,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-3</v>
       </c>
@@ -35289,8 +35289,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-4</v>
       </c>
@@ -35328,8 +35328,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -35379,8 +35379,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-2-1</v>
       </c>
@@ -35414,8 +35414,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-3-1</v>
       </c>
@@ -35449,8 +35449,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-4-1</v>
       </c>
@@ -35484,8 +35484,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-5-1</v>
       </c>
@@ -35519,8 +35519,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -35559,8 +35559,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -35594,8 +35594,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -35631,8 +35631,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -35668,8 +35668,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-2-1</v>
       </c>
@@ -35703,8 +35703,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -35740,8 +35740,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -35777,8 +35777,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -35832,8 +35832,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -35883,8 +35883,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -35934,8 +35934,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -35975,8 +35975,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -36010,8 +36010,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -36047,8 +36047,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -36084,8 +36084,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -36119,8 +36119,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -36156,8 +36156,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -36197,8 +36197,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-2-1</v>
       </c>
@@ -36232,8 +36232,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-3-1</v>
       </c>
@@ -36267,8 +36267,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-4-1</v>
       </c>
@@ -36302,8 +36302,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-5-1</v>
       </c>
@@ -36337,8 +36337,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -36374,8 +36374,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-2-1</v>
       </c>
@@ -36409,8 +36409,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-3-1</v>
       </c>
@@ -36444,8 +36444,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-4-1</v>
       </c>
@@ -36479,8 +36479,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-5-1</v>
       </c>
@@ -36514,8 +36514,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -36551,8 +36551,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -36594,8 +36594,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -36635,8 +36635,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -36670,8 +36670,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -36711,8 +36711,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -36752,8 +36752,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -36787,8 +36787,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -36830,8 +36830,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -36867,8 +36867,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -36902,8 +36902,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -36937,8 +36937,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -36974,8 +36974,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-2-1</v>
       </c>
@@ -37009,8 +37009,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-3-1</v>
       </c>
@@ -37044,8 +37044,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-4-1</v>
       </c>
@@ -37079,8 +37079,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-5-1</v>
       </c>
@@ -37114,8 +37114,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -37151,8 +37151,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-2-1</v>
       </c>
@@ -37186,8 +37186,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-3-1</v>
       </c>
@@ -37221,8 +37221,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-4-1</v>
       </c>
@@ -37256,8 +37256,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-5-1</v>
       </c>
@@ -37291,8 +37291,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -37328,8 +37328,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -37367,8 +37367,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -37408,8 +37408,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -37445,8 +37445,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -37480,8 +37480,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-3-1</v>
       </c>
@@ -37515,8 +37515,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -37558,8 +37558,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-2-1</v>
       </c>
@@ -37595,8 +37595,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-3-1</v>
       </c>
@@ -37630,8 +37630,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-4-1</v>
       </c>
@@ -37665,8 +37665,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -37702,8 +37702,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-2-1</v>
       </c>
@@ -37737,8 +37737,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -37776,8 +37776,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -37817,8 +37817,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -37854,8 +37854,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -37891,8 +37891,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -37928,8 +37928,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -37965,8 +37965,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -38002,8 +38002,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -38037,8 +38037,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -38072,8 +38072,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -38107,8 +38107,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -38142,8 +38142,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -38177,8 +38177,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -38216,8 +38216,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -38251,8 +38251,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -38288,8 +38288,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -38323,8 +38323,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -38358,8 +38358,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -38393,8 +38393,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -38428,8 +38428,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -38463,8 +38463,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -38498,8 +38498,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -38533,8 +38533,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -38568,8 +38568,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-10-1</v>
       </c>
@@ -38603,8 +38603,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-11-1</v>
       </c>
@@ -38638,8 +38638,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -38675,8 +38675,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-2-1</v>
       </c>
@@ -38710,8 +38710,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-3-1</v>
       </c>
@@ -38745,8 +38745,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-4-1</v>
       </c>
@@ -38780,8 +38780,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-5-1</v>
       </c>
@@ -38815,8 +38815,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-6-1</v>
       </c>
@@ -38850,8 +38850,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-7-1</v>
       </c>
@@ -38885,8 +38885,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -38922,8 +38922,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-2-1</v>
       </c>
@@ -38957,8 +38957,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-3-1</v>
       </c>
@@ -38992,8 +38992,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-4-1</v>
       </c>
@@ -39027,8 +39027,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-5-1</v>
       </c>
@@ -39062,8 +39062,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-6-1</v>
       </c>
@@ -39097,8 +39097,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-7-1</v>
       </c>
@@ -39132,8 +39132,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-8-1</v>
       </c>
@@ -39167,8 +39167,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-9-1</v>
       </c>
@@ -39202,8 +39202,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -39239,8 +39239,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -39276,8 +39276,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -39319,8 +39319,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -39358,8 +39358,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -39397,8 +39397,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -39440,8 +39440,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -39477,8 +39477,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-2-1</v>
       </c>
@@ -39512,8 +39512,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -39549,8 +39549,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -39584,8 +39584,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -39623,8 +39623,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -39664,8 +39664,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -39699,8 +39699,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -39734,8 +39734,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -39769,8 +39769,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -39804,8 +39804,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -39839,8 +39839,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -39874,8 +39874,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -39911,8 +39911,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -39950,8 +39950,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -39985,8 +39985,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -40020,8 +40020,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-4-1</v>
       </c>
@@ -40055,8 +40055,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-5-1</v>
       </c>
@@ -40090,8 +40090,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-6-1</v>
       </c>
@@ -40125,8 +40125,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-7-1</v>
       </c>
@@ -40160,8 +40160,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-8-1</v>
       </c>
@@ -40195,8 +40195,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-9-1</v>
       </c>
@@ -40230,8 +40230,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-10-1</v>
       </c>
@@ -40265,8 +40265,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-11-1</v>
       </c>
@@ -40300,8 +40300,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-12-1</v>
       </c>
@@ -40335,8 +40335,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-13-1</v>
       </c>
@@ -40370,8 +40370,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -40409,8 +40409,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-2-1</v>
       </c>
@@ -40444,8 +40444,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-3-1</v>
       </c>
@@ -40479,8 +40479,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-4-1</v>
       </c>
@@ -40514,8 +40514,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-5-1</v>
       </c>
@@ -40549,8 +40549,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-6-1</v>
       </c>
@@ -40584,8 +40584,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-7-1</v>
       </c>
@@ -40619,8 +40619,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-8-1</v>
       </c>
@@ -40654,8 +40654,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-9-1</v>
       </c>
@@ -40689,8 +40689,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-10-1</v>
       </c>
@@ -40724,8 +40724,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-11-1</v>
       </c>
@@ -40759,8 +40759,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-12-1</v>
       </c>
@@ -40794,8 +40794,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-13-1</v>
       </c>
@@ -40829,8 +40829,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-14-1</v>
       </c>
@@ -40864,8 +40864,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-15-1</v>
       </c>
@@ -40899,8 +40899,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -40936,8 +40936,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-2-1</v>
       </c>
@@ -40971,8 +40971,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-3-1</v>
       </c>
@@ -41006,8 +41006,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -41043,8 +41043,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -41080,8 +41080,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -41123,8 +41123,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -41160,8 +41160,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-2-1</v>
       </c>
@@ -41195,8 +41195,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-3-1</v>
       </c>
@@ -41230,8 +41230,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-4-1</v>
       </c>
@@ -41265,8 +41265,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-5-1</v>
       </c>
@@ -41300,8 +41300,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -41337,8 +41337,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-2-1</v>
       </c>
@@ -41372,8 +41372,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-3-1</v>
       </c>
@@ -41407,8 +41407,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-4-1</v>
       </c>
@@ -41442,8 +41442,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-5-1</v>
       </c>
@@ -41477,8 +41477,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -41514,8 +41514,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -41555,8 +41555,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -41598,8 +41598,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-2-1</v>
       </c>
@@ -41633,8 +41633,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -41672,8 +41672,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-2-1</v>
       </c>
@@ -41707,8 +41707,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -41748,8 +41748,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -41785,8 +41785,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -41822,8 +41822,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -41859,8 +41859,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -41898,8 +41898,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -41933,8 +41933,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -41970,8 +41970,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -42005,8 +42005,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -42040,8 +42040,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -42075,8 +42075,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -42110,8 +42110,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -42145,8 +42145,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -42180,8 +42180,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -42215,8 +42215,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-9-1</v>
       </c>
@@ -42250,8 +42250,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-10-1</v>
       </c>
@@ -42285,8 +42285,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-11-1</v>
       </c>
@@ -42320,8 +42320,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -42357,8 +42357,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-2-1</v>
       </c>
@@ -42392,8 +42392,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-3-1</v>
       </c>
@@ -42427,8 +42427,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-4-1</v>
       </c>
@@ -42462,8 +42462,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-5-1</v>
       </c>
@@ -42497,8 +42497,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-6-1</v>
       </c>
@@ -42532,8 +42532,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -42569,8 +42569,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -42604,8 +42604,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -42639,8 +42639,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -42674,8 +42674,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-5-1</v>
       </c>
@@ -42709,8 +42709,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-6-1</v>
       </c>
@@ -42744,8 +42744,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-7-1</v>
       </c>
@@ -42779,8 +42779,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-8-1</v>
       </c>
@@ -42814,8 +42814,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -42851,8 +42851,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -42894,8 +42894,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-2-1</v>
       </c>
@@ -42929,8 +42929,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-3-1</v>
       </c>
@@ -42964,8 +42964,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-4-1</v>
       </c>
@@ -42999,8 +42999,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -43040,8 +43040,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -43077,8 +43077,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -43114,8 +43114,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-1-1</v>
       </c>
@@ -43151,8 +43151,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-1-1</v>
       </c>
@@ -43190,8 +43190,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-2-1</v>
       </c>
@@ -43225,8 +43225,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F296),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F296)&gt;0)*ROW($F$11:F296),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J296),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-3-1</v>
       </c>
@@ -43260,8 +43260,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F297),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F297)&gt;0)*ROW($F$11:F297),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J297),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-4-1</v>
       </c>
@@ -43295,8 +43295,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F298),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F298)&gt;0)*ROW($F$11:F298),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J298),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-5-1</v>
       </c>
@@ -43330,8 +43330,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F299),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F299)&gt;0)*ROW($F$11:F299),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J299),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-6-1</v>
       </c>
@@ -43365,8 +43365,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F300),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F300)&gt;0)*ROW($F$11:F300),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J300),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-7-1</v>
       </c>
@@ -43400,8 +43400,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F301),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F301)&gt;0)*ROW($F$11:F301),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J301),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-8-1</v>
       </c>
@@ -43435,8 +43435,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F302),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F302)&gt;0)*ROW($F$11:F302),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J302),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-9-1</v>
       </c>
@@ -43470,8 +43470,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F303),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F303)&gt;0)*ROW($F$11:F303),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J303),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-1-1</v>
       </c>
@@ -43527,8 +43527,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F304),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F304)&gt;0)*ROW($F$11:F304),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J304),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-1-1</v>
       </c>
@@ -43580,8 +43580,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F305),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F305)&gt;0)*ROW($F$11:F305),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J305),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-1-2</v>
       </c>
@@ -43627,8 +43627,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F306),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F306)&gt;0)*ROW($F$11:F306),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J306),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-1-3</v>
       </c>
@@ -43674,8 +43674,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F307),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F307)&gt;0)*ROW($F$11:F307),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J307),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-1-1</v>
       </c>
@@ -43727,8 +43727,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F308),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F308)&gt;0)*ROW($F$11:F308),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J308),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-2-1</v>
       </c>
@@ -43776,8 +43776,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F309),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F309)&gt;0)*ROW($F$11:F309),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J309),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-3-1</v>
       </c>
@@ -43811,8 +43811,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F310),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F310)&gt;0)*ROW($F$11:F310),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J310),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-1-1</v>
       </c>
@@ -43850,8 +43850,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F311),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F311)&gt;0)*ROW($F$11:F311),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J311),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>107-1-1</v>
       </c>
@@ -43887,8 +43887,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F312),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F312)&gt;0)*ROW($F$11:F312),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J312),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-1</v>
       </c>
@@ -43940,8 +43940,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F313),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F313)&gt;0)*ROW($F$11:F313),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J313),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-2</v>
       </c>
@@ -43987,8 +43987,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F314),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F314)&gt;0)*ROW($F$11:F314),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J314),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-2-1</v>
       </c>
@@ -44036,8 +44036,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F315),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F315)&gt;0)*ROW($F$11:F315),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J315),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-3-1</v>
       </c>
@@ -44071,8 +44071,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F316),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F316)&gt;0)*ROW($F$11:F316),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J316),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-4-1</v>
       </c>
@@ -44106,8 +44106,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F317),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F317)&gt;0)*ROW($F$11:F317),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J317),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-5-1</v>
       </c>
@@ -44141,8 +44141,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F318),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F318)&gt;0)*ROW($F$11:F318),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J318),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-6-1</v>
       </c>
@@ -44176,8 +44176,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F319),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F319)&gt;0)*ROW($F$11:F319),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J319),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-7-1</v>
       </c>
@@ -44211,8 +44211,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F320),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F320)&gt;0)*ROW($F$11:F320),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J320),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-8-1</v>
       </c>
